--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6650-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6650-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ECD31D8-C7DB-4BD8-8B9E-2BA1745658A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6EBE0949-BAFD-48CF-AB54-445489116223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{D6811297-5901-4676-8134-8939CCC8E5BF}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E05F15CD-23A9-4E32-9CC0-54F4F1EBDB05}"/>
   </bookViews>
   <sheets>
     <sheet name="6650-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1505,25 +1505,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62EF9B95-9DDB-4966-8966-63D51EA038D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC919CC9-CB2F-4114-A0E5-F7A74DC8C2A3}">
   <dimension ref="A1:X21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1713,7 +1713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>8.26</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="41">
         <v>2022</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="43"/>
       <c r="B15" s="44"/>
       <c r="C15" s="20" t="s">
@@ -2473,7 +2473,7 @@
       <c r="W15" s="50"/>
       <c r="X15" s="46"/>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2021</v>
       </c>
@@ -2545,7 +2545,7 @@
         <v>6.45</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="39">
         <v>2020</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2019</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2018</v>
       </c>
@@ -2761,7 +2761,7 @@
         <v>8.3699999999999992</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2017</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39" t="s">
         <v>44</v>
       </c>
